--- a/wwwroot/templates/CariTemplate.xlsx
+++ b/wwwroot/templates/CariTemplate.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89973B4E-4D74-446D-90FB-04EEC0CB4525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03ED3BD-EC37-445A-860F-3F94EDBBA246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="2985" windowWidth="18825" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5685" yWindow="4485" windowWidth="16950" windowHeight="11115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
+  <si>
+    <t>CariId</t>
+  </si>
+  <si>
+    <t>CariGrupId</t>
+  </si>
   <si>
     <t>CariAdi</t>
   </si>
@@ -58,16 +64,157 @@
     <t>CariYetkiliMail</t>
   </si>
   <si>
-    <t>CariGrupId</t>
-  </si>
-  <si>
-    <t>CariId</t>
-  </si>
-  <si>
     <t>DovizKodu</t>
   </si>
   <si>
     <t>CariAktifPasif</t>
+  </si>
+  <si>
+    <t>ABC Gıda</t>
+  </si>
+  <si>
+    <t>ABC Gıda Sanayi ve Ticaret Ltd. Şti.</t>
+  </si>
+  <si>
+    <t>İkitelli OSB Mah. 12. Sok. No:5</t>
+  </si>
+  <si>
+    <t>İstanbul</t>
+  </si>
+  <si>
+    <t>Başakşehir</t>
+  </si>
+  <si>
+    <t>İkitelli</t>
+  </si>
+  <si>
+    <t>3456789012</t>
+  </si>
+  <si>
+    <t>www.abcgida.com</t>
+  </si>
+  <si>
+    <t>Ahmet Yılmaz</t>
+  </si>
+  <si>
+    <t>02125550001</t>
+  </si>
+  <si>
+    <t>05325550001</t>
+  </si>
+  <si>
+    <t>ahmet.yilmaz@abcgida.com</t>
+  </si>
+  <si>
+    <t>Mavi Yazılım</t>
+  </si>
+  <si>
+    <t>Mavi Yazılım Hizmetleri A.Ş.</t>
+  </si>
+  <si>
+    <t>Yıldız Teknik Üni. Teknopark B Blok No:14</t>
+  </si>
+  <si>
+    <t>Esenler</t>
+  </si>
+  <si>
+    <t>Davutpaşa</t>
+  </si>
+  <si>
+    <t>4567890123</t>
+  </si>
+  <si>
+    <t>www.maviyazilim.com</t>
+  </si>
+  <si>
+    <t>Ayşe Demir</t>
+  </si>
+  <si>
+    <t>02125550002</t>
+  </si>
+  <si>
+    <t>05325550002</t>
+  </si>
+  <si>
+    <t>ayse.demir@maviyazilim.com</t>
+  </si>
+  <si>
+    <t>Ege Medikal</t>
+  </si>
+  <si>
+    <t>Ege Medikal Ürünler Tic. Ltd. Şti.</t>
+  </si>
+  <si>
+    <t>Kazımdirik Mah. 296/2 Sok. No:18</t>
+  </si>
+  <si>
+    <t>İzmir</t>
+  </si>
+  <si>
+    <t>Bornova</t>
+  </si>
+  <si>
+    <t>5678901234</t>
+  </si>
+  <si>
+    <t>www.egemedikal.com</t>
+  </si>
+  <si>
+    <t>Mehmet Kaya</t>
+  </si>
+  <si>
+    <t>02325550003</t>
+  </si>
+  <si>
+    <t>05325550003</t>
+  </si>
+  <si>
+    <t>mehmet.kaya@egemedikal.com</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Anka Lojistik</t>
+  </si>
+  <si>
+    <t>Anka Lojistik ve Depolama A.Ş.</t>
+  </si>
+  <si>
+    <t>Saray Mah. Keresteciler Sitesi 3. Cad. No:27</t>
+  </si>
+  <si>
+    <t>Ankara</t>
+  </si>
+  <si>
+    <t>Kahramankazan</t>
+  </si>
+  <si>
+    <t>Kazan</t>
+  </si>
+  <si>
+    <t>6789012345</t>
+  </si>
+  <si>
+    <t>www.ankalojistik.com</t>
+  </si>
+  <si>
+    <t>Zeynep Çelik</t>
+  </si>
+  <si>
+    <t>03125550004</t>
+  </si>
+  <si>
+    <t>05325550004</t>
+  </si>
+  <si>
+    <t>zeynep.celik@ankalojistik.com</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>TL</t>
   </si>
 </sst>
 </file>
@@ -81,7 +228,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -108,16 +254,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
+    <cellStyle name="Köprü" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -130,7 +281,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -172,74 +323,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -247,55 +338,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -304,13 +355,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -344,24 +395,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -387,7 +427,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -416,82 +456,275 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" customWidth="1"/>
-    <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N2" s="1"/>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/wwwroot/templates/CariTemplate.xlsx
+++ b/wwwroot/templates/CariTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOD\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EMutabakat\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03ED3BD-EC37-445A-860F-3F94EDBBA246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D95F4B-286C-4191-917B-475252D1BB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="4485" windowWidth="16950" windowHeight="11115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7485" yWindow="1380" windowWidth="16950" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>3456789012</t>
   </si>
   <si>
-    <t>www.abcgida.com</t>
-  </si>
-  <si>
     <t>Ahmet Yılmaz</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>4567890123</t>
   </si>
   <si>
-    <t>www.maviyazilim.com</t>
-  </si>
-  <si>
     <t>Ayşe Demir</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>5678901234</t>
   </si>
   <si>
-    <t>www.egemedikal.com</t>
-  </si>
-  <si>
     <t>Mehmet Kaya</t>
   </si>
   <si>
@@ -196,9 +187,6 @@
     <t>6789012345</t>
   </si>
   <si>
-    <t>www.ankalojistik.com</t>
-  </si>
-  <si>
     <t>Zeynep Çelik</t>
   </si>
   <si>
@@ -215,6 +203,18 @@
   </si>
   <si>
     <t>TL</t>
+  </si>
+  <si>
+    <t>https://abcgida.com</t>
+  </si>
+  <si>
+    <t>https://maviyazilim.com</t>
+  </si>
+  <si>
+    <t>https://egemedikal.com</t>
+  </si>
+  <si>
+    <t>https://ankalojistik.com</t>
   </si>
 </sst>
 </file>
@@ -254,12 +254,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -552,23 +555,23 @@
       <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -582,43 +585,43 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -632,43 +635,43 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -682,49 +685,55 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="J5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="P5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{85A614E9-06B1-426D-9195-398702F2FF7D}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{DFD0F7D7-800B-4948-8FA3-19FCA6FEBCED}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{48E6E11E-AA42-4547-AD51-50A94EF1EC9D}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{3B6D6488-D37C-490D-877B-FD4D00B3385D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>